--- a/exports/trend_1d/NHPC_full_report.xlsx
+++ b/exports/trend_1d/NHPC_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>6.29</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42086</v>
+        <v>42087</v>
       </c>
       <c r="H2" t="n">
-        <v>19.6</v>
+        <v>19.35</v>
       </c>
       <c r="I2" t="n">
         <v>19.36504224848519</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K2" t="n">
-        <v>0.51</v>
+        <v>-0.77</v>
       </c>
       <c r="L2" t="n">
         <v>2.56</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>7.94</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42104</v>
+        <v>42107</v>
       </c>
       <c r="H3" t="n">
-        <v>20.65</v>
+        <v>20.95</v>
       </c>
       <c r="I3" t="n">
         <v>20.76011915118267</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.72</v>
+        <v>-8.27</v>
       </c>
       <c r="L3" t="n">
-        <v>7.24</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M3" t="n">
         <v>0.74</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>7.52</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42130</v>
+        <v>42131</v>
       </c>
       <c r="H4" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="I4" t="n">
         <v>19.39143934616734</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.92</v>
+        <v>-8.35</v>
       </c>
       <c r="L4" t="n">
-        <v>7.64</v>
+        <v>8.83</v>
       </c>
       <c r="M4" t="n">
         <v>0.5600000000000001</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>7.07</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42151</v>
+        <v>42152</v>
       </c>
       <c r="H5" t="n">
-        <v>19.5</v>
+        <v>20.2</v>
       </c>
       <c r="I5" t="n">
         <v>20.0408965669946</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.56</v>
+        <v>-5.21</v>
       </c>
       <c r="L5" t="n">
-        <v>1.82</v>
+        <v>7.03</v>
       </c>
       <c r="M5" t="n">
         <v>0.52</v>
       </c>
       <c r="N5" t="n">
-        <v>1.3</v>
+        <v>3.59</v>
       </c>
       <c r="O5" t="n">
         <v>-1.54</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>7.43</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42160</v>
+        <v>42163</v>
       </c>
       <c r="H6" t="n">
-        <v>19.14</v>
+        <v>18.85</v>
       </c>
       <c r="I6" t="n">
         <v>18.94597340355726</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.25</v>
+        <v>-6.68</v>
       </c>
       <c r="L6" t="n">
         <v>7.72</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.06</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42293</v>
+        <v>42296</v>
       </c>
       <c r="H7" t="n">
-        <v>17.45</v>
+        <v>17.6</v>
       </c>
       <c r="I7" t="n">
         <v>17.56698410442366</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K7" t="n">
-        <v>7.43</v>
+        <v>6.63</v>
       </c>
       <c r="L7" t="n">
         <v>7.43</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.39</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42381</v>
+        <v>42382</v>
       </c>
       <c r="H8" t="n">
-        <v>20.6</v>
+        <v>20.1</v>
       </c>
       <c r="I8" t="n">
         <v>20.13833714506429</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K8" t="n">
-        <v>17.05</v>
+        <v>14.2</v>
       </c>
       <c r="L8" t="n">
         <v>2.61</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>11.58</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42437</v>
+        <v>42438</v>
       </c>
       <c r="H9" t="n">
-        <v>20.9</v>
+        <v>21.45</v>
       </c>
       <c r="I9" t="n">
         <v>21.3493278582486</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.98</v>
+        <v>-6.72</v>
       </c>
       <c r="L9" t="n">
         <v>9.199999999999999</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>11.54</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42486</v>
+        <v>42487</v>
       </c>
       <c r="H10" t="n">
-        <v>23.1</v>
+        <v>21.55</v>
       </c>
       <c r="I10" t="n">
         <v>21.8434558756321</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K10" t="n">
-        <v>7.69</v>
+        <v>0.47</v>
       </c>
       <c r="L10" t="n">
         <v>3.96</v>
       </c>
       <c r="M10" t="n">
-        <v>1.86</v>
+        <v>5.63</v>
       </c>
       <c r="N10" t="n">
-        <v>5.39</v>
+        <v>6.71</v>
       </c>
       <c r="O10" t="n">
         <v>2.63</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>10.42</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42515</v>
+        <v>42516</v>
       </c>
       <c r="H11" t="n">
-        <v>22.3</v>
+        <v>22.65</v>
       </c>
       <c r="I11" t="n">
         <v>22.51190666844752</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.48</v>
+        <v>-5.1</v>
       </c>
       <c r="L11" t="n">
-        <v>3.94</v>
+        <v>5.8</v>
       </c>
       <c r="M11" t="n">
         <v>0.71</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.77</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42621</v>
+        <v>42622</v>
       </c>
       <c r="H12" t="n">
-        <v>26.7</v>
+        <v>26.2</v>
       </c>
       <c r="I12" t="n">
         <v>26.27779349462732</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K12" t="n">
-        <v>17.88</v>
+        <v>15.67</v>
       </c>
       <c r="L12" t="n">
         <v>2.65</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>8</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42698</v>
+        <v>42699</v>
       </c>
       <c r="H13" t="n">
-        <v>26.35</v>
+        <v>27.1</v>
       </c>
       <c r="I13" t="n">
         <v>26.88489274409694</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.57</v>
+        <v>-3.44</v>
       </c>
       <c r="L13" t="n">
-        <v>3.44</v>
+        <v>4.58</v>
       </c>
       <c r="M13" t="n">
         <v>1.9</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>11.08</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42754</v>
+        <v>42755</v>
       </c>
       <c r="H14" t="n">
-        <v>27.8</v>
+        <v>27.25</v>
       </c>
       <c r="I14" t="n">
         <v>27.45679053121458</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K14" t="n">
-        <v>2.58</v>
+        <v>0.55</v>
       </c>
       <c r="L14" t="n">
         <v>5.35</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>11.45</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42767</v>
+        <v>42768</v>
       </c>
       <c r="H15" t="n">
-        <v>29.25</v>
+        <v>30.85</v>
       </c>
       <c r="I15" t="n">
         <v>30.30835473247012</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>-7.34</v>
+        <v>-13.21</v>
       </c>
       <c r="L15" t="n">
-        <v>9.539999999999999</v>
+        <v>14.68</v>
       </c>
       <c r="M15" t="n">
         <v>0.72</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>12.16</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42872</v>
+        <v>42873</v>
       </c>
       <c r="H16" t="n">
-        <v>30.95</v>
+        <v>30.4</v>
       </c>
       <c r="I16" t="n">
         <v>30.83179384961449</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K16" t="n">
-        <v>0.32</v>
+        <v>-1.46</v>
       </c>
       <c r="L16" t="n">
         <v>5.19</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>7.07</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42893</v>
+        <v>42894</v>
       </c>
       <c r="H17" t="n">
-        <v>31.2</v>
+        <v>31.55</v>
       </c>
       <c r="I17" t="n">
         <v>31.31203474990201</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.63</v>
+        <v>-3.78</v>
       </c>
       <c r="L17" t="n">
-        <v>4.11</v>
+        <v>4.28</v>
       </c>
       <c r="M17" t="n">
         <v>1.14</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.06</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42915</v>
+        <v>42916</v>
       </c>
       <c r="H18" t="n">
-        <v>32.05</v>
+        <v>31.35</v>
       </c>
       <c r="I18" t="n">
         <v>31.42316249660614</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K18" t="n">
-        <v>1.58</v>
+        <v>-0.63</v>
       </c>
       <c r="L18" t="n">
         <v>1.58</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>10.25</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43021</v>
+        <v>43024</v>
       </c>
       <c r="H19" t="n">
-        <v>28.1</v>
+        <v>28.7</v>
       </c>
       <c r="I19" t="n">
         <v>28.53536278262467</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K19" t="n">
-        <v>10.37</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L19" t="n">
         <v>4.63</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>7.09</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43052</v>
+        <v>43053</v>
       </c>
       <c r="H20" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="I20" t="n">
         <v>27.14914576465266</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.23</v>
+        <v>-5.57</v>
       </c>
       <c r="L20" t="n">
         <v>6.45</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>9.92</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43077</v>
+        <v>43080</v>
       </c>
       <c r="H21" t="n">
-        <v>28.3</v>
+        <v>29</v>
       </c>
       <c r="I21" t="n">
         <v>28.89911083296231</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.43</v>
+        <v>-7.01</v>
       </c>
       <c r="L21" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="M21" t="n">
         <v>0.74</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>7.46</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43115</v>
+        <v>43116</v>
       </c>
       <c r="H22" t="n">
-        <v>31.6</v>
+        <v>30.3</v>
       </c>
       <c r="I22" t="n">
         <v>30.48281090341014</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K22" t="n">
-        <v>8.970000000000001</v>
+        <v>4.48</v>
       </c>
       <c r="L22" t="n">
         <v>4.48</v>
@@ -1695,7 +1958,7 @@
         <v>0.18</v>
       </c>
       <c r="N22" t="n">
-        <v>1.71</v>
+        <v>4.11</v>
       </c>
       <c r="O22" t="n">
         <v>2.47</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>11.64</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43192</v>
+        <v>43193</v>
       </c>
       <c r="H23" t="n">
-        <v>27.95</v>
+        <v>29.05</v>
       </c>
       <c r="I23" t="n">
         <v>28.0945019398455</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K23" t="n">
-        <v>7.76</v>
+        <v>4.13</v>
       </c>
       <c r="L23" t="n">
         <v>4.62</v>
@@ -1752,7 +2027,7 @@
         <v>1.25</v>
       </c>
       <c r="N23" t="n">
-        <v>3.76</v>
+        <v>3.94</v>
       </c>
       <c r="O23" t="n">
         <v>-4.11</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>10.26</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43235</v>
+        <v>43236</v>
       </c>
       <c r="H24" t="n">
-        <v>26.7</v>
+        <v>26.4</v>
       </c>
       <c r="I24" t="n">
         <v>26.47775060294836</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K24" t="n">
-        <v>-8.09</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>8.43</v>
+        <v>10.33</v>
       </c>
       <c r="M24" t="n">
         <v>0.71</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>7.12</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43321</v>
+        <v>43322</v>
       </c>
       <c r="H25" t="n">
-        <v>24.5</v>
+        <v>24.95</v>
       </c>
       <c r="I25" t="n">
         <v>24.90515348908141</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K25" t="n">
-        <v>7.2</v>
+        <v>5.49</v>
       </c>
       <c r="L25" t="n">
         <v>4.36</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>8.06</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43362</v>
+        <v>43364</v>
       </c>
       <c r="H26" t="n">
-        <v>24.15</v>
+        <v>23.75</v>
       </c>
       <c r="I26" t="n">
         <v>24.12718246738926</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.21</v>
+        <v>-4.81</v>
       </c>
       <c r="L26" t="n">
-        <v>4.21</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M26" t="n">
         <v>0.8</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>8.68</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43410</v>
+        <v>43413</v>
       </c>
       <c r="H27" t="n">
-        <v>24.65</v>
+        <v>26.45</v>
       </c>
       <c r="I27" t="n">
         <v>24.79183746707103</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.79</v>
+        <v>-11.37</v>
       </c>
       <c r="L27" t="n">
-        <v>4.84</v>
+        <v>13.26</v>
       </c>
       <c r="M27" t="n">
-        <v>0.87</v>
+        <v>1.42</v>
       </c>
       <c r="N27" t="n">
-        <v>4.87</v>
+        <v>7.3</v>
       </c>
       <c r="O27" t="n">
         <v>-1.66</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>10.92</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43490</v>
+        <v>43493</v>
       </c>
       <c r="H28" t="n">
-        <v>25</v>
+        <v>24.55</v>
       </c>
       <c r="I28" t="n">
         <v>24.97672567277808</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K28" t="n">
-        <v>-5.48</v>
+        <v>-7.18</v>
       </c>
       <c r="L28" t="n">
-        <v>6.05</v>
+        <v>7.37</v>
       </c>
       <c r="M28" t="n">
         <v>3.69</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>6.48</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43531</v>
+        <v>43532</v>
       </c>
       <c r="H29" t="n">
-        <v>24.8</v>
+        <v>25.15</v>
       </c>
       <c r="I29" t="n">
         <v>25.14393875053841</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.02</v>
+        <v>-2.44</v>
       </c>
       <c r="L29" t="n">
         <v>5.5</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>9.49</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43571</v>
+        <v>43573</v>
       </c>
       <c r="H30" t="n">
-        <v>24</v>
+        <v>23.65</v>
       </c>
       <c r="I30" t="n">
         <v>23.69805492639686</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.57</v>
+        <v>-5.96</v>
       </c>
       <c r="L30" t="n">
-        <v>4.97</v>
+        <v>6.36</v>
       </c>
       <c r="M30" t="n">
         <v>0.79</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>6.31</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43609</v>
+        <v>43612</v>
       </c>
       <c r="H31" t="n">
-        <v>23.05</v>
+        <v>23.6</v>
       </c>
       <c r="I31" t="n">
         <v>23.4826849278691</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K31" t="n">
-        <v>2.54</v>
+        <v>0.21</v>
       </c>
       <c r="L31" t="n">
         <v>1.9</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>8.25</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43663</v>
+        <v>43664</v>
       </c>
       <c r="H32" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="I32" t="n">
         <v>23.49226088693985</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K32" t="n">
-        <v>0.85</v>
+        <v>-0.85</v>
       </c>
       <c r="L32" t="n">
         <v>2.54</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>7.03</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43691</v>
+        <v>43693</v>
       </c>
       <c r="H33" t="n">
-        <v>22.85</v>
+        <v>23.15</v>
       </c>
       <c r="I33" t="n">
         <v>23.04131731835356</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K33" t="n">
-        <v>2.35</v>
+        <v>1.07</v>
       </c>
       <c r="L33" t="n">
         <v>1.92</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>8.77</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43732</v>
+        <v>43733</v>
       </c>
       <c r="H34" t="n">
-        <v>23.15</v>
+        <v>22.75</v>
       </c>
       <c r="I34" t="n">
         <v>22.81007263444798</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>-1.73</v>
       </c>
       <c r="L34" t="n">
         <v>2.38</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43749</v>
+        <v>43752</v>
       </c>
       <c r="H35" t="n">
-        <v>23.05</v>
+        <v>23.7</v>
       </c>
       <c r="I35" t="n">
         <v>23.59728110266887</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.32</v>
+        <v>-4.18</v>
       </c>
       <c r="L35" t="n">
-        <v>2.2</v>
+        <v>4.62</v>
       </c>
       <c r="M35" t="n">
         <v>0.65</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>9.75</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43859</v>
+        <v>43860</v>
       </c>
       <c r="H36" t="n">
-        <v>26.15</v>
+        <v>25.2</v>
       </c>
       <c r="I36" t="n">
         <v>25.37071730988652</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K36" t="n">
-        <v>10.34</v>
+        <v>6.33</v>
       </c>
       <c r="L36" t="n">
         <v>3.59</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>18.25</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44062</v>
+        <v>44063</v>
       </c>
       <c r="H37" t="n">
-        <v>20.9</v>
+        <v>23.55</v>
       </c>
       <c r="I37" t="n">
         <v>20.93212336080175</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K37" t="n">
-        <v>17.06</v>
+        <v>6.55</v>
       </c>
       <c r="L37" t="n">
         <v>4.76</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>138</v>
+        <v>139</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>7</v>
+      </c>
+      <c r="U37" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>13.58</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44071</v>
+        <v>44074</v>
       </c>
       <c r="H38" t="n">
-        <v>22.7</v>
+        <v>21.65</v>
       </c>
       <c r="I38" t="n">
         <v>21.67227990916545</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.61</v>
+        <v>-8.07</v>
       </c>
       <c r="L38" t="n">
         <v>12.1</v>
@@ -2607,7 +3062,7 @@
         <v>0.24</v>
       </c>
       <c r="N38" t="n">
-        <v>2.2</v>
+        <v>4.63</v>
       </c>
       <c r="O38" t="n">
         <v>12.68</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>14.87</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44140</v>
+        <v>44141</v>
       </c>
       <c r="H39" t="n">
-        <v>20.6</v>
+        <v>21.7</v>
       </c>
       <c r="I39" t="n">
         <v>20.95143855069911</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K39" t="n">
-        <v>4.85</v>
+        <v>-0.23</v>
       </c>
       <c r="L39" t="n">
         <v>7.39</v>
@@ -2664,7 +3131,7 @@
         <v>2.54</v>
       </c>
       <c r="N39" t="n">
-        <v>2.66</v>
+        <v>5.34</v>
       </c>
       <c r="O39" t="n">
         <v>-4.63</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,25 +3179,25 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44223</v>
+        <v>44224</v>
       </c>
       <c r="H40" t="n">
-        <v>23.45</v>
+        <v>23</v>
       </c>
       <c r="I40" t="n">
         <v>23.04868948822883</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K40" t="n">
-        <v>8.06</v>
+        <v>5.99</v>
       </c>
       <c r="L40" t="n">
         <v>5.99</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4</v>
+        <v>0.85</v>
       </c>
       <c r="N40" t="n">
         <v>4.42</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>9.58</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44239</v>
+        <v>44242</v>
       </c>
       <c r="H41" t="n">
-        <v>25.05</v>
+        <v>25.25</v>
       </c>
       <c r="I41" t="n">
         <v>25.20231218898623</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>-8.91</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="L41" t="n">
         <v>10.65</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>7.54</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44249</v>
+        <v>44250</v>
       </c>
       <c r="H42" t="n">
-        <v>24.05</v>
+        <v>23.75</v>
       </c>
       <c r="I42" t="n">
         <v>23.76231872080186</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.75</v>
+        <v>-5.94</v>
       </c>
       <c r="L42" t="n">
-        <v>5.54</v>
+        <v>6.34</v>
       </c>
       <c r="M42" t="n">
         <v>3.87</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>10.95</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44258</v>
+        <v>44259</v>
       </c>
       <c r="H43" t="n">
-        <v>24.8</v>
+        <v>25.95</v>
       </c>
       <c r="I43" t="n">
         <v>25.8458051872819</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.42</v>
+        <v>-9.26</v>
       </c>
       <c r="L43" t="n">
-        <v>6.53</v>
+        <v>12.21</v>
       </c>
       <c r="M43" t="n">
         <v>1.41</v>
       </c>
       <c r="N43" t="n">
-        <v>2.32</v>
+        <v>4.64</v>
       </c>
       <c r="O43" t="n">
         <v>-1.25</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>12.18</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44526</v>
+        <v>44529</v>
       </c>
       <c r="H44" t="n">
-        <v>30.65</v>
+        <v>30.3</v>
       </c>
       <c r="I44" t="n">
         <v>30.33494387119705</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K44" t="n">
-        <v>18.11</v>
+        <v>16.76</v>
       </c>
       <c r="L44" t="n">
         <v>11.18</v>
       </c>
       <c r="M44" t="n">
-        <v>1.32</v>
+        <v>2.12</v>
       </c>
       <c r="N44" t="n">
         <v>5.14</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>180</v>
+        <v>181</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>10</v>
+      </c>
+      <c r="U44" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>11.75</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44655</v>
+        <v>44656</v>
       </c>
       <c r="H45" t="n">
-        <v>28.5</v>
+        <v>29.6</v>
       </c>
       <c r="I45" t="n">
         <v>29.40796738426967</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K45" t="n">
-        <v>5.94</v>
+        <v>2.31</v>
       </c>
       <c r="L45" t="n">
         <v>15.18</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>5</v>
+      </c>
+      <c r="U45" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>10.96</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44691</v>
+        <v>44692</v>
       </c>
       <c r="H46" t="n">
-        <v>31.95</v>
+        <v>30.6</v>
       </c>
       <c r="I46" t="n">
         <v>31.74205986248928</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K46" t="n">
-        <v>7.94</v>
+        <v>3.38</v>
       </c>
       <c r="L46" t="n">
         <v>4.39</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>18.75</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44754</v>
+        <v>44755</v>
       </c>
       <c r="H47" t="n">
-        <v>33</v>
+        <v>33.45</v>
       </c>
       <c r="I47" t="n">
         <v>33.0852400753413</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K47" t="n">
-        <v>-7.84</v>
+        <v>-9.31</v>
       </c>
       <c r="L47" t="n">
         <v>12.42</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44911</v>
+        <v>44914</v>
       </c>
       <c r="H48" t="n">
-        <v>41</v>
+        <v>40.15</v>
       </c>
       <c r="I48" t="n">
         <v>40.25763356395553</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="K48" t="n">
-        <v>22.57</v>
+        <v>20.03</v>
       </c>
       <c r="L48" t="n">
         <v>2.09</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>6</v>
+      </c>
+      <c r="U48" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>10.15</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44943</v>
+        <v>44944</v>
       </c>
       <c r="H49" t="n">
-        <v>40.95</v>
+        <v>42.05</v>
       </c>
       <c r="I49" t="n">
         <v>41.6710765094766</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.99</v>
+        <v>-4.73</v>
       </c>
       <c r="L49" t="n">
-        <v>3.74</v>
+        <v>5.85</v>
       </c>
       <c r="M49" t="n">
         <v>1.28</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44964</v>
+        <v>44965</v>
       </c>
       <c r="H50" t="n">
-        <v>40.2</v>
+        <v>40.15</v>
       </c>
       <c r="I50" t="n">
         <v>40.18593610778191</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K50" t="n">
-        <v>-4.4</v>
+        <v>-4.52</v>
       </c>
       <c r="L50" t="n">
         <v>5.47</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44991</v>
+        <v>44993</v>
       </c>
       <c r="H51" t="n">
-        <v>39.95</v>
+        <v>41.65</v>
       </c>
       <c r="I51" t="n">
         <v>41.48551140288529</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K51" t="n">
-        <v>0.5</v>
+        <v>-3.74</v>
       </c>
       <c r="L51" t="n">
-        <v>2.37</v>
+        <v>4.11</v>
       </c>
       <c r="M51" t="n">
         <v>1.82</v>
       </c>
       <c r="N51" t="n">
-        <v>2.43</v>
+        <v>4.26</v>
       </c>
       <c r="O51" t="n">
         <v>-0.12</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>10.76</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45230</v>
+        <v>45231</v>
       </c>
       <c r="H52" t="n">
-        <v>50.2</v>
+        <v>49.5</v>
       </c>
       <c r="I52" t="n">
         <v>49.59769233235258</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K52" t="n">
-        <v>20.53</v>
+        <v>18.85</v>
       </c>
       <c r="L52" t="n">
         <v>7.08</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>160</v>
+        <v>161</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>9</v>
+      </c>
+      <c r="U52" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45250</v>
+        <v>45251</v>
       </c>
       <c r="H53" t="n">
-        <v>52.8</v>
+        <v>54.4</v>
       </c>
       <c r="I53" t="n">
         <v>54.30462990362425</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>-6.67</v>
+        <v>-9.9</v>
       </c>
       <c r="L53" t="n">
-        <v>8.08</v>
+        <v>11.41</v>
       </c>
       <c r="M53" t="n">
         <v>0.91</v>
       </c>
       <c r="N53" t="n">
-        <v>2.02</v>
+        <v>3.03</v>
       </c>
       <c r="O53" t="n">
         <v>-1.39</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45331</v>
+        <v>45334</v>
       </c>
       <c r="H54" t="n">
-        <v>96.25</v>
+        <v>81</v>
       </c>
       <c r="I54" t="n">
         <v>87.5443350774473</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K54" t="n">
-        <v>76.93000000000001</v>
+        <v>48.9</v>
       </c>
       <c r="L54" t="n">
         <v>3.95</v>
@@ -3519,7 +4166,7 @@
         <v>5.48</v>
       </c>
       <c r="N54" t="n">
-        <v>6.94</v>
+        <v>15.84</v>
       </c>
       <c r="O54" t="n">
         <v>3.03</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>36.39</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="H55" t="n">
-        <v>93.40000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="I55" t="n">
         <v>96.08324144146465</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K55" t="n">
-        <v>-15.31</v>
+        <v>-18.77</v>
       </c>
       <c r="L55" t="n">
         <v>22.1</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>10.07</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H56" t="n">
-        <v>113.15</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I56" t="n">
         <v>98.78793837852652</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K56" t="n">
-        <v>17.62</v>
+        <v>1.25</v>
       </c>
       <c r="L56" t="n">
         <v>6.03</v>
@@ -3633,7 +4304,7 @@
         <v>2.27</v>
       </c>
       <c r="N56" t="n">
-        <v>5.26</v>
+        <v>13.92</v>
       </c>
       <c r="O56" t="n">
         <v>3</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>26.06</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45482</v>
+        <v>45483</v>
       </c>
       <c r="H57" t="n">
-        <v>106.05</v>
+        <v>108.82</v>
       </c>
       <c r="I57" t="n">
         <v>108.6572139162432</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K57" t="n">
-        <v>-8.880000000000001</v>
+        <v>-11.72</v>
       </c>
       <c r="L57" t="n">
         <v>16.27</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>12.41</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45496</v>
+        <v>45497</v>
       </c>
       <c r="H58" t="n">
-        <v>103.75</v>
+        <v>102.38</v>
       </c>
       <c r="I58" t="n">
         <v>103.3844184702516</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K58" t="n">
-        <v>-4.66</v>
+        <v>-5.92</v>
       </c>
       <c r="L58" t="n">
         <v>11.17</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>16.21</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45632</v>
+        <v>45635</v>
       </c>
       <c r="H59" t="n">
-        <v>84.87</v>
+        <v>86.77</v>
       </c>
       <c r="I59" t="n">
         <v>85.72156023920942</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K59" t="n">
-        <v>17.1</v>
+        <v>15.25</v>
       </c>
       <c r="L59" t="n">
         <v>4.9</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>6</v>
+      </c>
+      <c r="U59" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45660</v>
+        <v>45663</v>
       </c>
       <c r="H60" t="n">
-        <v>83.09</v>
+        <v>79.27</v>
       </c>
       <c r="I60" t="n">
         <v>79.43966343903092</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K60" t="n">
-        <v>-4.24</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="L60" t="n">
         <v>9.68</v>
@@ -3861,7 +4580,7 @@
         <v>2.8</v>
       </c>
       <c r="N60" t="n">
-        <v>3.52</v>
+        <v>4.6</v>
       </c>
       <c r="O60" t="n">
         <v>2.24</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>10.98</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45736</v>
+        <v>45737</v>
       </c>
       <c r="H61" t="n">
-        <v>80.04000000000001</v>
+        <v>82.56</v>
       </c>
       <c r="I61" t="n">
         <v>80.92099582322842</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.97</v>
+        <v>-4.15</v>
       </c>
       <c r="L61" t="n">
-        <v>4.81</v>
+        <v>6.08</v>
       </c>
       <c r="M61" t="n">
         <v>1.8</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>9.56</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45782</v>
+        <v>45783</v>
       </c>
       <c r="H62" t="n">
-        <v>84.63</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="I62" t="n">
         <v>81.89310262312023</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K62" t="n">
-        <v>2.51</v>
+        <v>-1.03</v>
       </c>
       <c r="L62" t="n">
         <v>8.25</v>
@@ -3975,7 +4718,7 @@
         <v>7.88</v>
       </c>
       <c r="N62" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="O62" t="n">
         <v>3.15</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>11.21</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45792</v>
+        <v>45793</v>
       </c>
       <c r="H63" t="n">
-        <v>86.95</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="I63" t="n">
         <v>87.08651068869722</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K63" t="n">
-        <v>-6.41</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>7.01</v>
+        <v>11.1</v>
       </c>
       <c r="M63" t="n">
         <v>4.64</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>11.27</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45825</v>
+        <v>45826</v>
       </c>
       <c r="H64" t="n">
-        <v>85.06999999999999</v>
+        <v>82.53</v>
       </c>
       <c r="I64" t="n">
         <v>84.28460834192504</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K64" t="n">
-        <v>-5.17</v>
+        <v>-8</v>
       </c>
       <c r="L64" t="n">
-        <v>5.61</v>
+        <v>8.48</v>
       </c>
       <c r="M64" t="n">
         <v>2.93</v>
       </c>
       <c r="N64" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="O64" t="n">
         <v>3.17</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>9.81</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="H65" t="n">
-        <v>82.28</v>
+        <v>83.5</v>
       </c>
       <c r="I65" t="n">
         <v>82.81078325348061</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K65" t="n">
-        <v>0.3</v>
+        <v>-1.18</v>
       </c>
       <c r="L65" t="n">
         <v>8.75</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>4</v>
+      </c>
+      <c r="U65" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>6.83</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="H66" t="n">
-        <v>82.84999999999999</v>
+        <v>81.48</v>
       </c>
       <c r="I66" t="n">
         <v>82.41466559285266</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.78</v>
+        <v>-2.42</v>
       </c>
       <c r="L66" t="n">
-        <v>2.13</v>
+        <v>3.89</v>
       </c>
       <c r="M66" t="n">
         <v>0.79</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>6.59</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="H67" t="n">
-        <v>78.58</v>
+        <v>79.22</v>
       </c>
       <c r="I67" t="n">
         <v>78.75615933486843</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K67" t="n">
-        <v>3.56</v>
+        <v>2.77</v>
       </c>
       <c r="L67" t="n">
         <v>1.68</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>5.83</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H68" t="n">
-        <v>79.42</v>
+        <v>77.56999999999999</v>
       </c>
       <c r="I68" t="n">
         <v>78.49626605484217</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K68" t="n">
-        <v>0.25</v>
+        <v>-2.08</v>
       </c>
       <c r="L68" t="n">
-        <v>1.14</v>
+        <v>2.63</v>
       </c>
       <c r="M68" t="n">
         <v>0.9</v>
       </c>
       <c r="N68" t="n">
-        <v>1.78</v>
+        <v>2.33</v>
       </c>
       <c r="O68" t="n">
         <v>0.8100000000000001</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>8.57</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H69" t="n">
-        <v>77.66</v>
+        <v>80.58</v>
       </c>
       <c r="I69" t="n">
         <v>77.95875463150074</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.12</v>
+        <v>-3.88</v>
       </c>
       <c r="L69" t="n">
-        <v>3.78</v>
+        <v>5</v>
       </c>
       <c r="M69" t="n">
         <v>3.02</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>4</v>
+      </c>
+      <c r="U69" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>9.17</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H70" t="n">
-        <v>79.19</v>
+        <v>76.77</v>
       </c>
       <c r="I70" t="n">
         <v>77.80022873219029</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K70" t="n">
-        <v>-1.72</v>
+        <v>-4.73</v>
       </c>
       <c r="L70" t="n">
-        <v>2.76</v>
+        <v>4.94</v>
       </c>
       <c r="M70" t="n">
         <v>0.7</v>
       </c>
       <c r="N70" t="n">
-        <v>2.49</v>
+        <v>3.06</v>
       </c>
       <c r="O70" t="n">
         <v>3.76</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>10.24</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="H71" t="n">
-        <v>77.90000000000001</v>
+        <v>79.31</v>
       </c>
       <c r="I71" t="n">
         <v>78.9024213257382</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K71" t="n">
-        <v>-1.47</v>
+        <v>-3.31</v>
       </c>
       <c r="L71" t="n">
         <v>6.41</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="H72" t="n">
-        <v>76.55</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="I72" t="n">
         <v>76.01325625127954</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K72" t="n">
-        <v>-3.48</v>
+        <v>-5.66</v>
       </c>
       <c r="L72" t="n">
-        <v>5.13</v>
+        <v>5.66</v>
       </c>
       <c r="M72" t="n">
         <v>1.34</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>4</v>
+      </c>
+      <c r="U72" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -4605,6 +5480,14 @@
       <c r="Q73" t="n">
         <v>41</v>
       </c>
+      <c r="R73" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9563,7 +10446,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.2</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="6">
@@ -9573,7 +10456,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -9583,7 +10466,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8">
@@ -9593,7 +10476,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -9603,7 +10486,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -9613,7 +10496,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11">
@@ -9653,7 +10536,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
@@ -9663,7 +10546,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.74</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="16">
@@ -9673,7 +10556,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.37</v>
+        <v>-3.36</v>
       </c>
     </row>
     <row r="17">
@@ -9683,7 +10566,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>76.93000000000001</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="18">
@@ -9693,7 +10576,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.1</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="19">
@@ -9703,7 +10586,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.94</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="20">
@@ -9713,7 +10596,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.13</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="21">
@@ -9733,7 +10616,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
@@ -9743,7 +10626,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -9753,7 +10636,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="25">
@@ -9773,7 +10656,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.05</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="27">
@@ -9783,7 +10666,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>15.18</v>
+        <v>15.84</v>
       </c>
     </row>
     <row r="28">
@@ -9793,7 +10676,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
